--- a/artfynd/A 67013-2021 artfynd.xlsx
+++ b/artfynd/A 67013-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 67013-2021 artfynd.xlsx
+++ b/artfynd/A 67013-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>60449570</v>
       </c>
       <c r="B2" t="n">
-        <v>104643</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534835.8836000346</v>
+        <v>534836</v>
       </c>
       <c r="R2" t="n">
-        <v>6607197.523107417</v>
+        <v>6607198</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,19 +754,9 @@
           <t>2016-07-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-07-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -805,6 +790,346 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>60449585</v>
+      </c>
+      <c r="B3" t="n">
+        <v>107708</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>245</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Campanula cervicaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>NV Lilla Rönningen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>534798</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6607222</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fellingsbro</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2016-07-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2016-07-06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kenneth Nordberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kenneth Nordberg, Tina Nordberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>79740537</v>
+      </c>
+      <c r="B4" t="n">
+        <v>107708</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>245</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Campanula cervicaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stentorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>534830</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6607186</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fellingsbro</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-08-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-08-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Innerslänt ett Exemplar</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sarah J Leander</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sarah J Leander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>81547856</v>
+      </c>
+      <c r="B5" t="n">
+        <v>107708</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>245</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Campanula cervicaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stentorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>534797</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6607216</v>
+      </c>
+      <c r="S5" t="n">
+        <v>26</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fellingsbro</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-06-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-06-03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>20-tal på västra sidan. Innerslänt, dikesbotten och ytterslänt.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sarah J Leander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sarah J Leander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 67013-2021 artfynd.xlsx
+++ b/artfynd/A 67013-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60449570</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60449585</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79740537</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1130,8 +1150,19 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81547856</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>